--- a/demo/dedup-demo.xlsx
+++ b/demo/dedup-demo.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="74">
   <si>
     <t>Last Name</t>
   </si>
@@ -37,9 +37,6 @@
     <t>Juan</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
     <t>1952-03-14</t>
   </si>
   <si>
@@ -55,9 +52,6 @@
     <t>Maria</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>1985-07-22</t>
   </si>
   <si>
@@ -70,7 +64,7 @@
     <t>Pedro</t>
   </si>
   <si>
-    <t>P</t>
+    <t>Poblete</t>
   </si>
   <si>
     <t>1988-03-21</t>
@@ -658,301 +652,295 @@
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
         <v>23</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
         <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" t="s">
         <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
         <v>34</v>
       </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B9" t="s">
+      <c r="E9" t="s">
         <v>38</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" t="s">
-        <v>40</v>
-      </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
         <v>41</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
         <v>49</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>53</v>
-      </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
         <v>54</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" t="s">
-        <v>58</v>
-      </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s">
         <v>59</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="F14" t="s">
         <v>62</v>
-      </c>
-      <c r="E14" t="s">
-        <v>63</v>
-      </c>
-      <c r="F14" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
         <v>65</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="F15" t="s">
         <v>68</v>
-      </c>
-      <c r="E15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s">
         <v>71</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" t="s">
         <v>73</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>